--- a/tabtools/qa/baseline/workbooks/effecttab_from_matrix.xlsx
+++ b/tabtools/qa/baseline/workbooks/effecttab_from_matrix.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="17">
   <si>
     <t>Refactor Baseline: effecttab matrix</t>
   </si>
@@ -21,581 +21,793 @@
     <t/>
   </si>
   <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
     <t>OR</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>-0.50</t>
   </si>
   <si>
     <t>(95% CI)</t>
   </si>
   <si>
+    <t>(0.80, 2.20)</t>
+  </si>
+  <si>
+    <t>(1.10, 3.50)</t>
+  </si>
+  <si>
+    <t>(-1.20, 0.20)</t>
+  </si>
+  <si>
     <t>p</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="133">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="187">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -648,8 +860,44 @@
       <b/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="56">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -906,28 +1154,8 @@
         <fgColor rgb="FFDBE5F1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="107">
+  <borders count="146">
     <border>
       <left/>
       <right/>
@@ -1041,6 +1269,27 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -1432,6 +1681,27 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="none"/>
       <top style="thin"/>
@@ -1447,6 +1717,27 @@
     </border>
     <border>
       <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="none"/>
@@ -1457,6 +1748,27 @@
       <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1474,6 +1786,132 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="none"/>
@@ -1509,65 +1947,30 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -1582,27 +1985,62 @@
       <left style="thin"/>
       <right style="thin"/>
       <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="thin"/>
+      <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="thin"/>
+      <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin"/>
-      <top style="thin"/>
+      <top style="none"/>
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
@@ -1639,13 +2077,76 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -1710,15 +2211,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1730,15 +2231,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1749,36 +2250,36 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1789,268 +2290,424 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="8" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="9" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="10" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="11" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="55" fillId="11" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="12" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="56" fillId="12" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="13" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="57" fillId="13" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="14" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="58" fillId="14" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="15" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="16" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="17" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="61" fillId="17" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="18" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="19" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="65" fillId="19" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="67" fillId="20" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="21" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="69" fillId="21" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="22" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="23" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="70" fillId="22" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="23" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="24" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="72" fillId="24" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="25" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="73" fillId="25" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="26" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="74" fillId="26" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="27" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="75" fillId="27" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="76" fillId="28" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="29" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="77" fillId="29" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="30" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="78" fillId="30" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="31" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="79" fillId="31" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="32" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="80" fillId="32" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="33" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="81" fillId="33" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="34" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="82" fillId="34" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="35" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="83" fillId="35" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="84" fillId="36" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="37" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="85" fillId="37" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="38" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="39" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="38" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="39" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="40" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="41" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="40" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="41" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="42" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="42" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="43" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="100" fillId="43" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="44" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="44" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="45" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="46" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="47" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="48" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="45" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="133" fillId="49" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="46" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="135" fillId="50" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="47" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="137" fillId="51" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="48" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="49" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="50" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="51" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="52" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="53" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="54" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="55" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2062,65 +2719,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="4.7109375" style="3" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="4" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="5" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="6" customWidth="true"/>
+    <col min="2" max="2" width="5.7109375" style="3" customWidth="true"/>
+    <col min="3" max="3" width="8.7109375" style="4" customWidth="true"/>
+    <col min="4" max="4" width="16.7109375" style="5" customWidth="true"/>
+    <col min="5" max="5" width="8.7109375" style="6" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="105" t="s">
+      <c r="D1" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="136" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="E2" s="111" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="115" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="116" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="117" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="C4" s="137" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="138" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="101" t="s">
+      <c r="C5" s="140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="141" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="142" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="127" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="128" t="s">
         <v>4</v>
+      </c>
+      <c r="C6" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="144" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="145" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
